--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -115,24 +115,12 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">12103</t>
   </si>
   <si>
     <t xml:space="preserve">Río Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
@@ -301,6 +289,12 @@
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">5105</t>
   </si>
   <si>
@@ -1240,6 +1234,12 @@
     <t xml:space="preserve">Coquimbo</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4201</t>
   </si>
   <si>
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:20</t>
+    <t xml:space="preserve">2026-09-09 20:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2840,10 +2840,10 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2861,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>67.24</v>
+        <v>66.67</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2872,10 +2872,10 @@
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2893,7 +2893,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>66.67</v>
+        <v>63.93</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2904,10 +2904,10 @@
         <v>2018</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>36</v>
@@ -2925,7 +2925,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>65.79</v>
+        <v>63.35</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2936,10 +2936,10 @@
         <v>2018</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2957,7 +2957,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>63.93</v>
+        <v>63.18</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2989,7 +2989,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>63.35</v>
+        <v>62.54</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -3000,10 +3000,10 @@
         <v>2018</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>42</v>
@@ -3021,7 +3021,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>63.18</v>
+        <v>60.38</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3053,7 +3053,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>62.54</v>
+        <v>50</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3064,28 +3064,28 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>60.38</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3096,28 +3096,28 @@
         <v>2018</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>50</v>
+        <v>69.06</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3131,25 +3131,25 @@
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>70</v>
+        <v>68.25</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3163,7 +3163,7 @@
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -3172,16 +3172,16 @@
         <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>69.06</v>
+        <v>67.58</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3192,28 +3192,28 @@
         <v>2018</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>68.25</v>
+        <v>67.21</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3224,28 +3224,28 @@
         <v>2018</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>67.58</v>
+        <v>66.21</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3259,7 +3259,7 @@
         <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>62</v>
@@ -3268,16 +3268,16 @@
         <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>67.21</v>
+        <v>65.36</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3288,28 +3288,28 @@
         <v>2018</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>66.21</v>
+        <v>65.3</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3323,25 +3323,25 @@
         <v>5</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>65.36</v>
+        <v>64.86</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3355,7 +3355,7 @@
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3364,16 +3364,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>65.3</v>
+        <v>64.71</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3384,10 +3384,10 @@
         <v>2018</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3396,16 +3396,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>64.86</v>
+        <v>64.54</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3419,7 +3419,7 @@
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3428,16 +3428,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>64.71</v>
+        <v>64.25</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3451,7 +3451,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3460,16 +3460,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>64.54</v>
+        <v>64.17</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3480,10 +3480,10 @@
         <v>2018</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3492,16 +3492,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>64.25</v>
+        <v>64.14</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3515,7 +3515,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3524,16 +3524,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>64.17</v>
+        <v>64.09</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3544,28 +3544,28 @@
         <v>2018</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>64.14</v>
+        <v>63.81</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3576,28 +3576,28 @@
         <v>2018</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>64.09</v>
+        <v>63.51</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3608,10 +3608,10 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3620,16 +3620,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>63.81</v>
+        <v>63.31</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3643,7 +3643,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3652,16 +3652,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>63.51</v>
+        <v>63.01</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3672,10 +3672,10 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3684,16 +3684,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>63.31</v>
+        <v>62.97</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3707,7 +3707,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3716,16 +3716,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>63.01</v>
+        <v>62.91</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3736,10 +3736,10 @@
         <v>2018</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3748,16 +3748,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>62.91</v>
+        <v>62.84</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3768,10 +3768,10 @@
         <v>2018</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3780,16 +3780,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>62.84</v>
+        <v>62.81</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3803,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3812,16 +3812,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>62.81</v>
+        <v>62.76</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3832,10 +3832,10 @@
         <v>2018</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3844,16 +3844,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>62.76</v>
+        <v>62.41</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3864,10 +3864,10 @@
         <v>2018</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3876,16 +3876,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>62.41</v>
+        <v>62.34</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3896,10 +3896,10 @@
         <v>2018</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3908,16 +3908,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>62.34</v>
+        <v>62</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3928,10 +3928,10 @@
         <v>2018</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3940,16 +3940,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>62</v>
+        <v>61.88</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3963,7 +3963,7 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3972,16 +3972,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>61.88</v>
+        <v>61.75</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3992,10 +3992,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -4004,16 +4004,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>61.75</v>
+        <v>61.51</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4024,10 +4024,10 @@
         <v>2018</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -4036,16 +4036,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>61.51</v>
+        <v>61.49</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4059,7 +4059,7 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -4068,16 +4068,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>61.49</v>
+        <v>61.32</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4088,10 +4088,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -4100,16 +4100,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>61.32</v>
+        <v>61.31</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4123,7 +4123,7 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -4132,16 +4132,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>61.31</v>
+        <v>61.19</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4152,10 +4152,10 @@
         <v>2018</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -4164,16 +4164,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>61.19</v>
+        <v>61.16</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4187,7 +4187,7 @@
         <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -4196,16 +4196,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>61.16</v>
+        <v>61.15</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4219,7 +4219,7 @@
         <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -4228,16 +4228,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>61.15</v>
+        <v>61.03</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4248,10 +4248,10 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -4260,16 +4260,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>61.03</v>
+        <v>60.99</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4283,7 +4283,7 @@
         <v>5</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -4292,16 +4292,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>60.99</v>
+        <v>60.85</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4312,10 +4312,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -4324,16 +4324,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>60.85</v>
+        <v>60.82</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4344,10 +4344,10 @@
         <v>2018</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4356,16 +4356,16 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>60.82</v>
+        <v>60.77</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4376,10 +4376,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4388,16 +4388,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>60.77</v>
+        <v>60.74</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4411,7 +4411,7 @@
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4420,16 +4420,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>60.74</v>
+        <v>60.66</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4440,28 +4440,28 @@
         <v>2018</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>60.66</v>
+        <v>60.37</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4472,10 +4472,10 @@
         <v>2018</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4484,16 +4484,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>60.37</v>
+        <v>60.25</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4507,7 +4507,7 @@
         <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4516,16 +4516,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>60.25</v>
+        <v>60.07</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4539,7 +4539,7 @@
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4548,16 +4548,16 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>60.07</v>
+        <v>60.05</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4568,10 +4568,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4580,16 +4580,16 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>60.05</v>
+        <v>60.04</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4600,10 +4600,10 @@
         <v>2018</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4612,16 +4612,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>60.04</v>
+        <v>59.92</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4632,10 +4632,10 @@
         <v>2018</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
@@ -4644,16 +4644,16 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>59.92</v>
+        <v>59.91</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4664,10 +4664,10 @@
         <v>2018</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>153</v>
@@ -4676,16 +4676,16 @@
         <v>154</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>59.91</v>
+        <v>59.88</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4696,28 +4696,28 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>155</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>156</v>
+        <v>46</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>59.88</v>
+        <v>59.82</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4731,25 +4731,25 @@
         <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>59.82</v>
+        <v>59.64</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4763,7 +4763,7 @@
         <v>7</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4772,16 +4772,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>59.64</v>
+        <v>59.58</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4792,10 +4792,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4804,16 +4804,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>59.58</v>
+        <v>59.54</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4824,10 +4824,10 @@
         <v>2018</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4836,16 +4836,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>59.54</v>
+        <v>59.47</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4856,10 +4856,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4868,16 +4868,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>59.47</v>
+        <v>59.44</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4888,10 +4888,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4900,10 +4900,10 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4923,7 +4923,7 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4932,16 +4932,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>59.44</v>
+        <v>59.43</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4952,10 +4952,10 @@
         <v>2018</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4964,16 +4964,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>59.43</v>
+        <v>59.26</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4984,10 +4984,10 @@
         <v>2018</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4996,16 +4996,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>59.26</v>
+        <v>59.21</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -5016,10 +5016,10 @@
         <v>2018</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -5028,16 +5028,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>59.21</v>
+        <v>58.98</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5051,7 +5051,7 @@
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5060,16 +5060,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>58.98</v>
+        <v>58.88</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5080,10 +5080,10 @@
         <v>2018</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5092,16 +5092,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>58.88</v>
+        <v>58.78</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5112,10 +5112,10 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5124,16 +5124,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>58.78</v>
+        <v>58.58</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5144,10 +5144,10 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5156,16 +5156,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>58.58</v>
+        <v>58.5</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5179,7 +5179,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5188,16 +5188,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>58.5</v>
+        <v>58.47</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5208,10 +5208,10 @@
         <v>2018</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5220,16 +5220,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>58.47</v>
+        <v>58.42</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5240,10 +5240,10 @@
         <v>2018</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5252,16 +5252,16 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>58.42</v>
+        <v>58.34</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5272,10 +5272,10 @@
         <v>2018</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5284,16 +5284,16 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>58.34</v>
+        <v>58.25</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5304,10 +5304,10 @@
         <v>2018</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5316,16 +5316,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>58.25</v>
+        <v>58.15</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5336,10 +5336,10 @@
         <v>2018</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5348,16 +5348,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>58.15</v>
+        <v>58.05</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5368,10 +5368,10 @@
         <v>2018</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5380,16 +5380,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>58.05</v>
+        <v>57.95</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5400,10 +5400,10 @@
         <v>2018</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5412,16 +5412,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>57.95</v>
+        <v>57.92</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5432,10 +5432,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5444,16 +5444,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>57.92</v>
+        <v>57.89</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5464,10 +5464,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5476,10 +5476,10 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5499,7 +5499,7 @@
         <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5508,16 +5508,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>57.89</v>
+        <v>57.88</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5528,10 +5528,10 @@
         <v>2018</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5540,16 +5540,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>57.88</v>
+        <v>57.82</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5563,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5572,16 +5572,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>57.82</v>
+        <v>57.73</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5592,10 +5592,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5604,16 +5604,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>57.73</v>
+        <v>57.65</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5624,10 +5624,10 @@
         <v>2018</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5636,16 +5636,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>57.65</v>
+        <v>57.6</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5656,10 +5656,10 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5668,16 +5668,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>57.6</v>
+        <v>57.2</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5688,10 +5688,10 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5700,16 +5700,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>57.2</v>
+        <v>57.19</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5723,7 +5723,7 @@
         <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5732,16 +5732,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>57.19</v>
+        <v>56.98</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5755,7 +5755,7 @@
         <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5764,16 +5764,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>56.98</v>
+        <v>56.96</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5784,10 +5784,10 @@
         <v>2018</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5796,16 +5796,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>56.96</v>
+        <v>56.88</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5816,10 +5816,10 @@
         <v>2018</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5828,16 +5828,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>56.88</v>
+        <v>56.87</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5851,7 +5851,7 @@
         <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5860,16 +5860,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>56.87</v>
+        <v>56.71</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5883,7 +5883,7 @@
         <v>6</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5892,16 +5892,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>56.71</v>
+        <v>56.69</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5912,10 +5912,10 @@
         <v>2018</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5924,16 +5924,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>56.69</v>
+        <v>56.65</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5947,7 +5947,7 @@
         <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5956,16 +5956,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>56.65</v>
+        <v>56.63</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5979,7 +5979,7 @@
         <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5988,16 +5988,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>56.63</v>
+        <v>56.6</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -6008,10 +6008,10 @@
         <v>2018</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6020,16 +6020,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>56.6</v>
+        <v>56.49</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6043,7 +6043,7 @@
         <v>6</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6052,16 +6052,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>56.49</v>
+        <v>56.42</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6072,10 +6072,10 @@
         <v>2018</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6084,16 +6084,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>56.42</v>
+        <v>56.38</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6107,7 +6107,7 @@
         <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6116,16 +6116,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>56.38</v>
+        <v>56.36</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6136,10 +6136,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6148,16 +6148,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>56.36</v>
+        <v>56.35</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6168,10 +6168,10 @@
         <v>2018</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6180,16 +6180,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>56.35</v>
+        <v>56.15</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6200,10 +6200,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6212,16 +6212,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>56.15</v>
+        <v>56.13</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6232,10 +6232,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6244,16 +6244,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>56.13</v>
+        <v>56.09</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6264,10 +6264,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6276,16 +6276,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>56.09</v>
+        <v>56.06</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6296,10 +6296,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6308,16 +6308,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>56.06</v>
+        <v>55.94</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6328,10 +6328,10 @@
         <v>2018</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6340,16 +6340,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>55.94</v>
+        <v>55.84</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6360,10 +6360,10 @@
         <v>2018</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6372,16 +6372,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>55.84</v>
+        <v>55.78</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6395,7 +6395,7 @@
         <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6404,16 +6404,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>55.78</v>
+        <v>55.56</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6424,10 +6424,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6436,16 +6436,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>55.56</v>
+        <v>55.5</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6456,10 +6456,10 @@
         <v>2018</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6468,16 +6468,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>55.5</v>
+        <v>55.37</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6488,10 +6488,10 @@
         <v>2018</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6500,16 +6500,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>55.37</v>
+        <v>55.3</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6523,7 +6523,7 @@
         <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6532,16 +6532,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>55.3</v>
+        <v>55.18</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6552,10 +6552,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>140</v>
+        <v>46</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6564,16 +6564,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>55.18</v>
+        <v>55.16</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6584,10 +6584,10 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6596,16 +6596,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>55.16</v>
+        <v>55</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6616,10 +6616,10 @@
         <v>2018</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6628,16 +6628,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>55</v>
+        <v>54.96</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6648,10 +6648,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6660,16 +6660,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>54.96</v>
+        <v>54.92</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6683,7 +6683,7 @@
         <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6692,16 +6692,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>54.92</v>
+        <v>54.82</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6712,10 +6712,10 @@
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6724,16 +6724,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>54.82</v>
+        <v>54.75</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6744,10 +6744,10 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6756,16 +6756,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>54.75</v>
+        <v>54.74</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6776,10 +6776,10 @@
         <v>2018</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6788,10 +6788,10 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6811,7 +6811,7 @@
         <v>16</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6820,16 +6820,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>54.74</v>
+        <v>54.56</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6840,10 +6840,10 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6852,16 +6852,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>54.56</v>
+        <v>54.51</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6875,7 +6875,7 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6884,16 +6884,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>54.51</v>
+        <v>54.49</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6907,7 +6907,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6916,16 +6916,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>54.49</v>
+        <v>54.26</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6936,10 +6936,10 @@
         <v>2018</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6948,16 +6948,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>54.26</v>
+        <v>54.14</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6971,7 +6971,7 @@
         <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6980,16 +6980,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>54.14</v>
+        <v>53.8</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -7000,10 +7000,10 @@
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7012,10 +7012,10 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7032,10 +7032,10 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7044,16 +7044,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>53.8</v>
+        <v>53.77</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7064,10 +7064,10 @@
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7076,16 +7076,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>53.77</v>
+        <v>53.74</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7099,7 +7099,7 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7108,16 +7108,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>53.74</v>
+        <v>53.67</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7131,7 +7131,7 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7140,16 +7140,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>53.67</v>
+        <v>53.57</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7163,7 +7163,7 @@
         <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7172,16 +7172,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>53.57</v>
+        <v>53.56</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7195,7 +7195,7 @@
         <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7204,16 +7204,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>53.56</v>
+        <v>53.46</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7224,10 +7224,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7236,16 +7236,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>53.46</v>
+        <v>53.35</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7259,7 +7259,7 @@
         <v>6</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7268,16 +7268,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>53.35</v>
+        <v>53.26</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7291,7 +7291,7 @@
         <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7300,16 +7300,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>53.26</v>
+        <v>53.05</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7320,10 +7320,10 @@
         <v>2018</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7332,16 +7332,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>53.05</v>
+        <v>52.91</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7352,10 +7352,10 @@
         <v>2018</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7364,16 +7364,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>52.91</v>
+        <v>52.79</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7384,10 +7384,10 @@
         <v>2018</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7396,16 +7396,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>52.79</v>
+        <v>52.78</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7416,10 +7416,10 @@
         <v>2018</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7428,16 +7428,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>52.78</v>
+        <v>52.76</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7448,10 +7448,10 @@
         <v>2018</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7460,16 +7460,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>52.76</v>
+        <v>52.31</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7480,10 +7480,10 @@
         <v>2018</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7492,16 +7492,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>52.31</v>
+        <v>52.29</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7512,10 +7512,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7524,16 +7524,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>52.29</v>
+        <v>52</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7544,10 +7544,10 @@
         <v>2018</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7556,16 +7556,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>52</v>
+        <v>51.81</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7576,10 +7576,10 @@
         <v>2018</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7588,16 +7588,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>51.81</v>
+        <v>51.51</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7608,10 +7608,10 @@
         <v>2018</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7620,16 +7620,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>51.51</v>
+        <v>51.18</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7643,7 +7643,7 @@
         <v>5</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7652,16 +7652,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>51.18</v>
+        <v>51.17</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7672,10 +7672,10 @@
         <v>2018</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7684,16 +7684,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>51.17</v>
+        <v>51.09</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7707,7 +7707,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7716,16 +7716,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>51.09</v>
+        <v>50.79</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7736,10 +7736,10 @@
         <v>2018</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7748,16 +7748,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>50.79</v>
+        <v>50.32</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7768,10 +7768,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7780,16 +7780,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>50.32</v>
+        <v>50.21</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7800,10 +7800,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7812,16 +7812,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>50.21</v>
+        <v>50.09</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7832,10 +7832,10 @@
         <v>2018</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7844,16 +7844,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>50.09</v>
+        <v>50.07</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7867,7 +7867,7 @@
         <v>13</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7876,16 +7876,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>50.07</v>
+        <v>49.76</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7896,10 +7896,10 @@
         <v>2018</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7908,16 +7908,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>49.76</v>
+        <v>49.69</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7928,10 +7928,10 @@
         <v>2018</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7940,16 +7940,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>49.69</v>
+        <v>49.67</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7963,7 +7963,7 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7972,16 +7972,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>49.67</v>
+        <v>49.46</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7995,7 +7995,7 @@
         <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -8004,16 +8004,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>49.46</v>
+        <v>49.31</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8027,7 +8027,7 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8036,16 +8036,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>49.31</v>
+        <v>49.15</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8059,7 +8059,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8068,16 +8068,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>49.15</v>
+        <v>49.06</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8088,10 +8088,10 @@
         <v>2018</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>140</v>
+        <v>57</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8100,16 +8100,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>49.06</v>
+        <v>48.91</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8120,10 +8120,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>61</v>
+        <v>138</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8132,16 +8132,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>48.91</v>
+        <v>48.77</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8155,7 +8155,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8164,16 +8164,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>48.77</v>
+        <v>48.13</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8184,10 +8184,10 @@
         <v>2018</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8196,16 +8196,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>48.13</v>
+        <v>46.42</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8216,10 +8216,10 @@
         <v>2018</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8228,16 +8228,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>46.42</v>
+        <v>46.1</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8251,7 +8251,7 @@
         <v>13</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8260,16 +8260,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>46.1</v>
+        <v>45.47</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8283,7 +8283,7 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8292,16 +8292,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>45.47</v>
+        <v>40.6</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8315,7 +8315,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8324,16 +8324,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>40.6</v>
+        <v>38.9</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8347,7 +8347,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>382</v>
@@ -8356,16 +8356,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>38.9</v>
+        <v>36.19</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8379,7 +8379,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>384</v>
@@ -8388,16 +8388,16 @@
         <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>36.19</v>
+        <v>34.36</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8411,7 +8411,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>386</v>
@@ -8420,16 +8420,16 @@
         <v>387</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>34.36</v>
+        <v>34.1</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8443,7 +8443,7 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>388</v>
@@ -8452,16 +8452,16 @@
         <v>389</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>34.1</v>
+        <v>29.43</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8475,7 +8475,7 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>390</v>
@@ -8484,16 +8484,16 @@
         <v>391</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>29.43</v>
+        <v>26.68</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8507,7 +8507,7 @@
         <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>392</v>
@@ -8516,16 +8516,16 @@
         <v>393</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>26.68</v>
+        <v>25.95</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8536,28 +8536,28 @@
         <v>2018</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>140</v>
+        <v>394</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>53</v>
+        <v>397</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>54</v>
+        <v>398</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>25.95</v>
+        <v>71.56</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8568,28 +8568,28 @@
         <v>2018</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="G189" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F189" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>71.56</v>
+        <v>69.77</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8603,7 +8603,7 @@
         <v>3</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>402</v>
@@ -8612,16 +8612,16 @@
         <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>69.77</v>
+        <v>69.38</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8632,28 +8632,28 @@
         <v>2018</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>69.38</v>
+        <v>68.06</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8667,7 +8667,7 @@
         <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>407</v>
@@ -8676,10 +8676,10 @@
         <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8699,7 +8699,7 @@
         <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>409</v>
@@ -8708,10 +8708,10 @@
         <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8740,10 +8740,10 @@
         <v>413</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8763,7 +8763,7 @@
         <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>414</v>
@@ -8772,10 +8772,10 @@
         <v>415</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8795,7 +8795,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>416</v>
@@ -8804,10 +8804,10 @@
         <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8827,7 +8827,7 @@
         <v>4</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
@@ -8836,10 +8836,10 @@
         <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8859,7 +8859,7 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8868,10 +8868,10 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8891,19 +8891,19 @@
         <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8932,10 +8932,10 @@
         <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8955,7 +8955,7 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>425</v>
@@ -8964,10 +8964,10 @@
         <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8987,7 +8987,7 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
@@ -8996,10 +8996,10 @@
         <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9019,7 +9019,7 @@
         <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>429</v>
@@ -9028,10 +9028,10 @@
         <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9051,7 +9051,7 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
@@ -9060,10 +9060,10 @@
         <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9083,7 +9083,7 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -9092,10 +9092,10 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9115,7 +9115,7 @@
         <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9124,10 +9124,10 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9147,7 +9147,7 @@
         <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9156,10 +9156,10 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9188,10 +9188,10 @@
         <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9211,7 +9211,7 @@
         <v>15</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>441</v>
@@ -9220,10 +9220,10 @@
         <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9243,7 +9243,7 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>443</v>
@@ -9252,10 +9252,10 @@
         <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9275,7 +9275,7 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>445</v>
@@ -9284,10 +9284,10 @@
         <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9316,10 +9316,10 @@
         <v>449</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9348,10 +9348,10 @@
         <v>451</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9371,7 +9371,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>452</v>
@@ -9380,10 +9380,10 @@
         <v>453</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9403,7 +9403,7 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>454</v>
@@ -9412,10 +9412,10 @@
         <v>455</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9444,10 +9444,10 @@
         <v>457</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9467,7 +9467,7 @@
         <v>3</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>458</v>
@@ -9476,10 +9476,10 @@
         <v>459</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9499,7 +9499,7 @@
         <v>15</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>460</v>
@@ -9508,10 +9508,10 @@
         <v>461</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9531,7 +9531,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>462</v>
@@ -9540,10 +9540,10 @@
         <v>463</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9572,10 +9572,10 @@
         <v>465</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9604,10 +9604,10 @@
         <v>467</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9636,10 +9636,10 @@
         <v>469</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9659,7 +9659,7 @@
         <v>4</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>470</v>
@@ -9668,10 +9668,10 @@
         <v>471</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9700,10 +9700,10 @@
         <v>473</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9732,10 +9732,10 @@
         <v>475</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9755,7 +9755,7 @@
         <v>15</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>476</v>
@@ -9764,10 +9764,10 @@
         <v>477</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9796,10 +9796,10 @@
         <v>447</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9828,10 +9828,10 @@
         <v>480</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:04</t>
+    <t xml:space="preserve">2026-09-18 11:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2018.xlsx
@@ -2125,7 +2125,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:26</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
